--- a/data-raw/clim1/keys/treatment-key-v5.xlsx
+++ b/data-raw/clim1/keys/treatment-key-v5.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC9926E-5023-44CF-B902-AD78B059BEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B0A60566-9079-413E-B9EC-7565B5D67D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
   <si>
     <t>trt_nu</t>
   </si>
@@ -228,6 +228,36 @@
   </si>
   <si>
     <t>sea_name</t>
+  </si>
+  <si>
+    <t>crop_names</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>borris</t>
+  </si>
+  <si>
+    <t>reimontra</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>p; leg1</t>
+  </si>
+  <si>
+    <t>p; leg2</t>
+  </si>
+  <si>
+    <t>p; buckwheat</t>
+  </si>
+  <si>
+    <t>p; a</t>
   </si>
 </sst>
 </file>
@@ -688,43 +718,43 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.88671875" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.88671875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="63.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="34" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
+    <col min="5" max="6" width="13.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="32.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="63.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>56</v>
       </c>
@@ -741,22 +771,25 @@
         <v>33</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
@@ -772,22 +805,25 @@
       <c r="E7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="6">
         <v>12.5</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="6">
+      <c r="I7" s="6">
         <v>300</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="6"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>35</v>
@@ -801,24 +837,27 @@
       <c r="E8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="6">
         <v>12.5</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <v>80</v>
       </c>
-      <c r="H8" s="6">
+      <c r="I8" s="6">
         <v>300</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="K8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>35</v>
@@ -832,22 +871,25 @@
       <c r="E9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="6">
         <v>25</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>80</v>
       </c>
-      <c r="H9" s="6">
+      <c r="I9" s="6">
         <v>300</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="6"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="6"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>35</v>
@@ -861,24 +903,27 @@
       <c r="E10" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="6">
         <v>12.5</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="6">
+      <c r="I10" s="6">
         <v>300</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="J10" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="K10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>35</v>
@@ -892,24 +937,27 @@
       <c r="E11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="6">
         <v>25</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="6">
+      <c r="I11" s="6">
         <v>300</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>35</v>
@@ -923,22 +971,25 @@
       <c r="E12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="6">
         <v>12.5</v>
       </c>
-      <c r="G12" s="7">
+      <c r="H12" s="7">
         <v>80</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K12" s="6"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>35</v>
@@ -952,24 +1003,27 @@
       <c r="E13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G13" s="5">
+      <c r="H13" s="5">
         <v>80</v>
       </c>
-      <c r="H13" s="5">
+      <c r="I13" s="5">
         <v>300</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="J13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="K13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>35</v>
@@ -983,22 +1037,25 @@
       <c r="E14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="4">
         <v>12.5</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>0</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="4">
         <v>300</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="J14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K14" s="4"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>35</v>
@@ -1012,22 +1069,25 @@
       <c r="E15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="4">
         <v>12.5</v>
       </c>
-      <c r="G15" s="4">
+      <c r="H15" s="4">
         <v>80</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="4">
         <v>300</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="J15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K15" s="4"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>35</v>
@@ -1041,22 +1101,25 @@
       <c r="E16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="4">
         <v>25</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>0</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <v>300</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="J16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K16" s="4"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>35</v>
@@ -1070,22 +1133,25 @@
       <c r="E17" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="4">
         <v>12.5</v>
       </c>
-      <c r="G17" s="4">
+      <c r="H17" s="4">
         <v>80</v>
       </c>
-      <c r="H17" s="4">
+      <c r="I17" s="4">
         <v>300</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="J17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="4"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K17" s="4"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>35</v>
@@ -1099,22 +1165,25 @@
       <c r="E18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="4">
         <v>25</v>
       </c>
-      <c r="G18" s="4">
+      <c r="H18" s="4">
         <v>80</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="4">
         <v>300</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="J18" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="4"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>35</v>
@@ -1128,22 +1197,25 @@
       <c r="E19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="4">
         <v>25</v>
       </c>
-      <c r="G19" s="4">
+      <c r="H19" s="4">
         <v>80</v>
       </c>
-      <c r="H19" s="4">
+      <c r="I19" s="4">
         <v>300</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K19" s="4"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>35</v>
@@ -1157,22 +1229,25 @@
       <c r="E20" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="4">
         <v>12.5</v>
       </c>
-      <c r="G20" s="4">
+      <c r="H20" s="4">
         <v>80</v>
       </c>
-      <c r="H20" s="4">
+      <c r="I20" s="4">
         <v>300</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="J20" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K20" s="4"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>35</v>
@@ -1186,22 +1261,25 @@
       <c r="E21" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="4">
         <v>25</v>
       </c>
-      <c r="G21" s="4">
+      <c r="H21" s="4">
         <v>80</v>
       </c>
-      <c r="H21" s="4">
+      <c r="I21" s="4">
         <v>300</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="4"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K21" s="4"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="4" t="s">
         <v>35</v>
@@ -1215,22 +1293,25 @@
       <c r="E22" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="5">
         <v>12.5</v>
       </c>
-      <c r="G22" s="5">
+      <c r="H22" s="5">
         <v>0</v>
       </c>
-      <c r="H22" s="5">
+      <c r="I22" s="5">
         <v>300</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="5"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K22" s="5"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="4" t="s">
         <v>35</v>
@@ -1244,22 +1325,25 @@
       <c r="E23" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="5">
         <v>12.5</v>
       </c>
-      <c r="G23" s="5">
+      <c r="H23" s="5">
         <v>80</v>
       </c>
-      <c r="H23" s="5">
+      <c r="I23" s="5">
         <v>300</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J23" s="5"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K23" s="5"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2">
@@ -1273,8 +1357,9 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2">
@@ -1288,8 +1373,9 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2">
@@ -1303,8 +1389,9 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2">
@@ -1318,8 +1405,9 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2">
@@ -1333,8 +1421,9 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2">
@@ -1348,8 +1437,9 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2">
@@ -1363,8 +1453,9 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2">
@@ -1378,8 +1469,9 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2">
@@ -1393,8 +1485,9 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2">
@@ -1408,8 +1501,9 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2">
@@ -1423,8 +1517,9 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2">
@@ -1438,8 +1533,9 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2">
@@ -1453,8 +1549,9 @@
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2">
@@ -1468,8 +1565,9 @@
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2">
@@ -1483,8 +1581,9 @@
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2">
@@ -1498,8 +1597,9 @@
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2">
@@ -1513,8 +1613,9 @@
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2">
@@ -1528,8 +1629,9 @@
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2">
@@ -1543,8 +1645,9 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2">
@@ -1558,8 +1661,9 @@
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2">
@@ -1573,8 +1677,9 @@
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2">
@@ -1588,8 +1693,9 @@
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2">
@@ -1603,8 +1709,9 @@
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2">
@@ -1618,8 +1725,9 @@
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2">
@@ -1633,8 +1741,9 @@
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2">
@@ -1648,8 +1757,9 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2">
@@ -1663,8 +1773,9 @@
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2">
@@ -1678,8 +1789,9 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2">
@@ -1693,8 +1805,9 @@
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2">
@@ -1708,8 +1821,9 @@
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2">
@@ -1723,8 +1837,9 @@
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2">
@@ -1738,26 +1853,27 @@
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C56" s="2">
         <v>50</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C57" s="2">
         <v>51</v>
       </c>
       <c r="D57" s="2"/>
-      <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1767,21 +1883,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"blankspreadsheet","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613AEFFE-C095-42A7-A0AC-5564FFC1D197}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408D0D6-C97A-426B-8466-DDDAA7A3F420}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7408D0D6-C97A-426B-8466-DDDAA7A3F420}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{613AEFFE-C095-42A7-A0AC-5564FFC1D197}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>